--- a/experiments/results/resnet18/CIFAR-100/ReAct/adaptive/max/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-100/ReAct/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -811,6 +811,153 @@
         <v>91.98999999999999</v>
       </c>
       <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>97.77</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>90.95999999999999</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>87.34999999999999</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>92.92</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=10.0,type=max</t>
         </is>
